--- a/baselines/svm-baseline/true_events.xlsx
+++ b/baselines/svm-baseline/true_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,49 +435,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99.3</v>
+        <v>49.05</v>
       </c>
       <c r="B2" t="n">
-        <v>99.95</v>
+        <v>53.85</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>eID_5</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>153.65</v>
+        <v>79.3</v>
       </c>
       <c r="B3" t="n">
-        <v>153.7</v>
+        <v>102.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>247.4</v>
+        <v>129.35</v>
       </c>
       <c r="B4" t="n">
-        <v>248.15</v>
+        <v>131.75</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>eID_4</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>277.55</v>
+        <v>152.8</v>
       </c>
       <c r="B5" t="n">
-        <v>278.15</v>
+        <v>157.4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -487,12 +487,129 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>297.1</v>
+        <v>171.2</v>
       </c>
       <c r="B6" t="n">
-        <v>297.45</v>
+        <v>172.75</v>
       </c>
       <c r="C6" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>182.85</v>
+      </c>
+      <c r="B7" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>196.6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>199.95</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>214.45</v>
+      </c>
+      <c r="B9" t="n">
+        <v>215.4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>243.65</v>
+      </c>
+      <c r="B10" t="n">
+        <v>246.9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>247.4</v>
+      </c>
+      <c r="B11" t="n">
+        <v>248.15</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>eID_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>253.3</v>
+      </c>
+      <c r="B12" t="n">
+        <v>254.4</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>267.1</v>
+      </c>
+      <c r="B13" t="n">
+        <v>271.65</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>277.1</v>
+      </c>
+      <c r="B14" t="n">
+        <v>283.65</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>294.6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>299.95</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>eID_1</t>
         </is>

--- a/baselines/svm-baseline/true_events.xlsx
+++ b/baselines/svm-baseline/true_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,62 +435,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>49.05</v>
+        <v>129.35</v>
       </c>
       <c r="B2" t="n">
-        <v>53.85</v>
+        <v>131.75</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79.3</v>
+        <v>152.8</v>
       </c>
       <c r="B3" t="n">
-        <v>102.5</v>
+        <v>157.4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>eID_5</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129.35</v>
+        <v>171.2</v>
       </c>
       <c r="B4" t="n">
-        <v>131.75</v>
+        <v>172.75</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>152.8</v>
+        <v>182.85</v>
       </c>
       <c r="B5" t="n">
-        <v>157.4</v>
+        <v>183.75</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>171.2</v>
+        <v>196.6</v>
       </c>
       <c r="B6" t="n">
-        <v>172.75</v>
+        <v>199.95</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -500,10 +500,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>182.85</v>
+        <v>214.45</v>
       </c>
       <c r="B7" t="n">
-        <v>183.75</v>
+        <v>215.4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>196.6</v>
+        <v>243.65</v>
       </c>
       <c r="B8" t="n">
-        <v>199.95</v>
+        <v>246.9</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -526,92 +526,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>214.45</v>
+        <v>253.3</v>
       </c>
       <c r="B9" t="n">
-        <v>215.4</v>
+        <v>254.4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>eID_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>243.65</v>
-      </c>
-      <c r="B10" t="n">
-        <v>246.9</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
           <t>eID_5</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>247.4</v>
-      </c>
-      <c r="B11" t="n">
-        <v>248.15</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>eID_4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>253.3</v>
-      </c>
-      <c r="B12" t="n">
-        <v>254.4</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>eID_5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>267.1</v>
-      </c>
-      <c r="B13" t="n">
-        <v>271.65</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>eID_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>277.1</v>
-      </c>
-      <c r="B14" t="n">
-        <v>283.65</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>eID_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>294.6</v>
-      </c>
-      <c r="B15" t="n">
-        <v>299.95</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>eID_1</t>
         </is>
       </c>
     </row>

--- a/baselines/svm-baseline/true_events.xlsx
+++ b/baselines/svm-baseline/true_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,106 +435,1905 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129.35</v>
+        <v>379.396</v>
       </c>
       <c r="B2" t="n">
-        <v>131.75</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>eID_1</t>
-        </is>
+        <v>380.296</v>
+      </c>
+      <c r="C2" t="n">
+        <v>405</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>152.8</v>
+        <v>380.363</v>
       </c>
       <c r="B3" t="n">
-        <v>157.4</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>eID_2</t>
-        </is>
+        <v>383.23</v>
+      </c>
+      <c r="C3" t="n">
+        <v>406</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>171.2</v>
+        <v>390.429</v>
       </c>
       <c r="B4" t="n">
-        <v>172.75</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>eID_5</t>
-        </is>
+        <v>391.263</v>
+      </c>
+      <c r="C4" t="n">
+        <v>405</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>182.85</v>
+        <v>392.696</v>
       </c>
       <c r="B5" t="n">
-        <v>183.75</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>eID_1</t>
-        </is>
+        <v>395.029</v>
+      </c>
+      <c r="C5" t="n">
+        <v>406</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>196.6</v>
+        <v>395.696</v>
       </c>
       <c r="B6" t="n">
-        <v>199.95</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>eID_5</t>
-        </is>
+        <v>396.163</v>
+      </c>
+      <c r="C6" t="n">
+        <v>412</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>214.45</v>
+        <v>431.029</v>
       </c>
       <c r="B7" t="n">
-        <v>215.4</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>eID_1</t>
-        </is>
+        <v>431.496</v>
+      </c>
+      <c r="C7" t="n">
+        <v>405</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>243.65</v>
+        <v>452.929</v>
       </c>
       <c r="B8" t="n">
-        <v>246.9</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>eID_5</t>
-        </is>
+        <v>453.529</v>
+      </c>
+      <c r="C8" t="n">
+        <v>405</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>253.3</v>
+        <v>453.829</v>
       </c>
       <c r="B9" t="n">
-        <v>254.4</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>eID_5</t>
-        </is>
+        <v>457.029</v>
+      </c>
+      <c r="C9" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>457.062</v>
+      </c>
+      <c r="B10" t="n">
+        <v>457.429</v>
+      </c>
+      <c r="C10" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>465.395</v>
+      </c>
+      <c r="B11" t="n">
+        <v>466.062</v>
+      </c>
+      <c r="C11" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>466.929</v>
+      </c>
+      <c r="B12" t="n">
+        <v>467.262</v>
+      </c>
+      <c r="C12" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>473.395</v>
+      </c>
+      <c r="B13" t="n">
+        <v>473.729</v>
+      </c>
+      <c r="C13" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>474.829</v>
+      </c>
+      <c r="B14" t="n">
+        <v>477.062</v>
+      </c>
+      <c r="C14" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>477.429</v>
+      </c>
+      <c r="B15" t="n">
+        <v>477.762</v>
+      </c>
+      <c r="C15" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>721.093</v>
+      </c>
+      <c r="B16" t="n">
+        <v>723.193</v>
+      </c>
+      <c r="C16" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>723.693</v>
+      </c>
+      <c r="B17" t="n">
+        <v>725.259</v>
+      </c>
+      <c r="C17" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>732.926</v>
+      </c>
+      <c r="B18" t="n">
+        <v>735.059</v>
+      </c>
+      <c r="C18" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>735.126</v>
+      </c>
+      <c r="B19" t="n">
+        <v>735.626</v>
+      </c>
+      <c r="C19" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>751.359</v>
+      </c>
+      <c r="B20" t="n">
+        <v>751.792</v>
+      </c>
+      <c r="C20" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>751.859</v>
+      </c>
+      <c r="B21" t="n">
+        <v>753.059</v>
+      </c>
+      <c r="C21" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>753.092</v>
+      </c>
+      <c r="B22" t="n">
+        <v>754.259</v>
+      </c>
+      <c r="C22" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>755.026</v>
+      </c>
+      <c r="B23" t="n">
+        <v>755.4589999999999</v>
+      </c>
+      <c r="C23" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>761.526</v>
+      </c>
+      <c r="B24" t="n">
+        <v>763.659</v>
+      </c>
+      <c r="C24" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>763.692</v>
+      </c>
+      <c r="B25" t="n">
+        <v>769.792</v>
+      </c>
+      <c r="C25" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>769.826</v>
+      </c>
+      <c r="B26" t="n">
+        <v>770.4589999999999</v>
+      </c>
+      <c r="C26" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>771.992</v>
+      </c>
+      <c r="B27" t="n">
+        <v>772.4589999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>772.8920000000001</v>
+      </c>
+      <c r="B28" t="n">
+        <v>773.492</v>
+      </c>
+      <c r="C28" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>773.559</v>
+      </c>
+      <c r="B29" t="n">
+        <v>773.792</v>
+      </c>
+      <c r="C29" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>780.4589999999999</v>
+      </c>
+      <c r="B30" t="n">
+        <v>781.059</v>
+      </c>
+      <c r="C30" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>781.126</v>
+      </c>
+      <c r="B31" t="n">
+        <v>784.992</v>
+      </c>
+      <c r="C31" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>785.625</v>
+      </c>
+      <c r="B32" t="n">
+        <v>786.8920000000001</v>
+      </c>
+      <c r="C32" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>787.025</v>
+      </c>
+      <c r="B33" t="n">
+        <v>788.825</v>
+      </c>
+      <c r="C33" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>788.925</v>
+      </c>
+      <c r="B34" t="n">
+        <v>789.259</v>
+      </c>
+      <c r="C34" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>789.325</v>
+      </c>
+      <c r="B35" t="n">
+        <v>789.759</v>
+      </c>
+      <c r="C35" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>789.859</v>
+      </c>
+      <c r="B36" t="n">
+        <v>800.525</v>
+      </c>
+      <c r="C36" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>801.025</v>
+      </c>
+      <c r="B37" t="n">
+        <v>801.425</v>
+      </c>
+      <c r="C37" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>869.225</v>
+      </c>
+      <c r="B38" t="n">
+        <v>870.191</v>
+      </c>
+      <c r="C38" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>875.625</v>
+      </c>
+      <c r="B39" t="n">
+        <v>875.891</v>
+      </c>
+      <c r="C39" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>875.925</v>
+      </c>
+      <c r="B40" t="n">
+        <v>877.591</v>
+      </c>
+      <c r="C40" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>877.625</v>
+      </c>
+      <c r="B41" t="n">
+        <v>878.458</v>
+      </c>
+      <c r="C41" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>882.491</v>
+      </c>
+      <c r="B42" t="n">
+        <v>893.2910000000001</v>
+      </c>
+      <c r="C42" t="n">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>895.158</v>
+      </c>
+      <c r="B43" t="n">
+        <v>896.158</v>
+      </c>
+      <c r="C43" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>897.091</v>
+      </c>
+      <c r="B44" t="n">
+        <v>899.391</v>
+      </c>
+      <c r="C44" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>901.224</v>
+      </c>
+      <c r="B45" t="n">
+        <v>901.824</v>
+      </c>
+      <c r="C45" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>902.8579999999999</v>
+      </c>
+      <c r="B46" t="n">
+        <v>904.258</v>
+      </c>
+      <c r="C46" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>905.191</v>
+      </c>
+      <c r="B47" t="n">
+        <v>905.891</v>
+      </c>
+      <c r="C47" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>908.724</v>
+      </c>
+      <c r="B48" t="n">
+        <v>909.524</v>
+      </c>
+      <c r="C48" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>909.591</v>
+      </c>
+      <c r="B49" t="n">
+        <v>910.924</v>
+      </c>
+      <c r="C49" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>911.8579999999999</v>
+      </c>
+      <c r="B50" t="n">
+        <v>913.391</v>
+      </c>
+      <c r="C50" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>913.424</v>
+      </c>
+      <c r="B51" t="n">
+        <v>914.424</v>
+      </c>
+      <c r="C51" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>914.491</v>
+      </c>
+      <c r="B52" t="n">
+        <v>916.658</v>
+      </c>
+      <c r="C52" t="n">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>916.724</v>
+      </c>
+      <c r="B53" t="n">
+        <v>918.557</v>
+      </c>
+      <c r="C53" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>918.624</v>
+      </c>
+      <c r="B54" t="n">
+        <v>919.891</v>
+      </c>
+      <c r="C54" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>923.224</v>
+      </c>
+      <c r="B55" t="n">
+        <v>924.2910000000001</v>
+      </c>
+      <c r="C55" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>924.324</v>
+      </c>
+      <c r="B56" t="n">
+        <v>925.7569999999999</v>
+      </c>
+      <c r="C56" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>925.7910000000001</v>
+      </c>
+      <c r="B57" t="n">
+        <v>927.991</v>
+      </c>
+      <c r="C57" t="n">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>928.024</v>
+      </c>
+      <c r="B58" t="n">
+        <v>929.2569999999999</v>
+      </c>
+      <c r="C58" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>929.2910000000001</v>
+      </c>
+      <c r="B59" t="n">
+        <v>929.824</v>
+      </c>
+      <c r="C59" t="n">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>929.891</v>
+      </c>
+      <c r="B60" t="n">
+        <v>931.2910000000001</v>
+      </c>
+      <c r="C60" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>931.724</v>
+      </c>
+      <c r="B61" t="n">
+        <v>932.391</v>
+      </c>
+      <c r="C61" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>934.691</v>
+      </c>
+      <c r="B62" t="n">
+        <v>935.2910000000001</v>
+      </c>
+      <c r="C62" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>936.124</v>
+      </c>
+      <c r="B63" t="n">
+        <v>937.391</v>
+      </c>
+      <c r="C63" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>937.424</v>
+      </c>
+      <c r="B64" t="n">
+        <v>941.357</v>
+      </c>
+      <c r="C64" t="n">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>941.424</v>
+      </c>
+      <c r="B65" t="n">
+        <v>943.891</v>
+      </c>
+      <c r="C65" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>943.924</v>
+      </c>
+      <c r="B66" t="n">
+        <v>944.2910000000001</v>
+      </c>
+      <c r="C66" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>947.124</v>
+      </c>
+      <c r="B67" t="n">
+        <v>948.691</v>
+      </c>
+      <c r="C67" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>949.324</v>
+      </c>
+      <c r="B68" t="n">
+        <v>952.89</v>
+      </c>
+      <c r="C68" t="n">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>955.924</v>
+      </c>
+      <c r="B69" t="n">
+        <v>957.157</v>
+      </c>
+      <c r="C69" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>957.824</v>
+      </c>
+      <c r="B70" t="n">
+        <v>958.59</v>
+      </c>
+      <c r="C70" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>961.824</v>
+      </c>
+      <c r="B71" t="n">
+        <v>962.2569999999999</v>
+      </c>
+      <c r="C71" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>963.224</v>
+      </c>
+      <c r="B72" t="n">
+        <v>966.657</v>
+      </c>
+      <c r="C72" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>966.6900000000001</v>
+      </c>
+      <c r="B73" t="n">
+        <v>968.824</v>
+      </c>
+      <c r="C73" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>969.6900000000001</v>
+      </c>
+      <c r="B74" t="n">
+        <v>970.224</v>
+      </c>
+      <c r="C74" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>971.724</v>
+      </c>
+      <c r="B75" t="n">
+        <v>972.557</v>
+      </c>
+      <c r="C75" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1003.123</v>
+      </c>
+      <c r="B76" t="n">
+        <v>1013.29</v>
+      </c>
+      <c r="C76" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1068.923</v>
+      </c>
+      <c r="B77" t="n">
+        <v>1069.589</v>
+      </c>
+      <c r="C77" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1069.623</v>
+      </c>
+      <c r="B78" t="n">
+        <v>1070.589</v>
+      </c>
+      <c r="C78" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>1071.623</v>
+      </c>
+      <c r="B79" t="n">
+        <v>1072.289</v>
+      </c>
+      <c r="C79" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1072.389</v>
+      </c>
+      <c r="B80" t="n">
+        <v>1073.189</v>
+      </c>
+      <c r="C80" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>1074.323</v>
+      </c>
+      <c r="B81" t="n">
+        <v>1075.123</v>
+      </c>
+      <c r="C81" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1075.523</v>
+      </c>
+      <c r="B82" t="n">
+        <v>1075.923</v>
+      </c>
+      <c r="C82" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1075.956</v>
+      </c>
+      <c r="B83" t="n">
+        <v>1077.323</v>
+      </c>
+      <c r="C83" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1077.389</v>
+      </c>
+      <c r="B84" t="n">
+        <v>1077.689</v>
+      </c>
+      <c r="C84" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>1077.723</v>
+      </c>
+      <c r="B85" t="n">
+        <v>1078.989</v>
+      </c>
+      <c r="C85" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>1079.023</v>
+      </c>
+      <c r="B86" t="n">
+        <v>1079.556</v>
+      </c>
+      <c r="C86" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1086.122</v>
+      </c>
+      <c r="B87" t="n">
+        <v>1086.989</v>
+      </c>
+      <c r="C87" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>1087.056</v>
+      </c>
+      <c r="B88" t="n">
+        <v>1087.589</v>
+      </c>
+      <c r="C88" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>1088.356</v>
+      </c>
+      <c r="B89" t="n">
+        <v>1088.622</v>
+      </c>
+      <c r="C89" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>1088.722</v>
+      </c>
+      <c r="B90" t="n">
+        <v>1089.989</v>
+      </c>
+      <c r="C90" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1090.489</v>
+      </c>
+      <c r="B91" t="n">
+        <v>1091.422</v>
+      </c>
+      <c r="C91" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1103.722</v>
+      </c>
+      <c r="B92" t="n">
+        <v>1105.156</v>
+      </c>
+      <c r="C92" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1105.422</v>
+      </c>
+      <c r="B93" t="n">
+        <v>1109.256</v>
+      </c>
+      <c r="C93" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1109.356</v>
+      </c>
+      <c r="B94" t="n">
+        <v>1109.989</v>
+      </c>
+      <c r="C94" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1115.822</v>
+      </c>
+      <c r="B95" t="n">
+        <v>1117.055</v>
+      </c>
+      <c r="C95" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1117.089</v>
+      </c>
+      <c r="B96" t="n">
+        <v>1122.422</v>
+      </c>
+      <c r="C96" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1137.222</v>
+      </c>
+      <c r="B97" t="n">
+        <v>1137.889</v>
+      </c>
+      <c r="C97" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1138.555</v>
+      </c>
+      <c r="B98" t="n">
+        <v>1139.389</v>
+      </c>
+      <c r="C98" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1139.789</v>
+      </c>
+      <c r="B99" t="n">
+        <v>1140.422</v>
+      </c>
+      <c r="C99" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1140.955</v>
+      </c>
+      <c r="B100" t="n">
+        <v>1141.889</v>
+      </c>
+      <c r="C100" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1142.389</v>
+      </c>
+      <c r="B101" t="n">
+        <v>1142.889</v>
+      </c>
+      <c r="C101" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1142.955</v>
+      </c>
+      <c r="B102" t="n">
+        <v>1143.989</v>
+      </c>
+      <c r="C102" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1144.022</v>
+      </c>
+      <c r="B103" t="n">
+        <v>1144.489</v>
+      </c>
+      <c r="C103" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1151.222</v>
+      </c>
+      <c r="B104" t="n">
+        <v>1154.722</v>
+      </c>
+      <c r="C104" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1173.222</v>
+      </c>
+      <c r="B105" t="n">
+        <v>1176.255</v>
+      </c>
+      <c r="C105" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1176.322</v>
+      </c>
+      <c r="B106" t="n">
+        <v>1177.322</v>
+      </c>
+      <c r="C106" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1182.722</v>
+      </c>
+      <c r="B107" t="n">
+        <v>1182.988</v>
+      </c>
+      <c r="C107" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>1184.521</v>
+      </c>
+      <c r="B108" t="n">
+        <v>1196.955</v>
+      </c>
+      <c r="C108" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1197.021</v>
+      </c>
+      <c r="B109" t="n">
+        <v>1199.255</v>
+      </c>
+      <c r="C109" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>1202.421</v>
+      </c>
+      <c r="B110" t="n">
+        <v>1203.288</v>
+      </c>
+      <c r="C110" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1203.321</v>
+      </c>
+      <c r="B111" t="n">
+        <v>1203.855</v>
+      </c>
+      <c r="C111" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1212.721</v>
+      </c>
+      <c r="B112" t="n">
+        <v>1213.088</v>
+      </c>
+      <c r="C112" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1213.121</v>
+      </c>
+      <c r="B113" t="n">
+        <v>1213.688</v>
+      </c>
+      <c r="C113" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1217.521</v>
+      </c>
+      <c r="B114" t="n">
+        <v>1253.354</v>
+      </c>
+      <c r="C114" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>1256.354</v>
+      </c>
+      <c r="B115" t="n">
+        <v>1257.254</v>
+      </c>
+      <c r="C115" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1257.321</v>
+      </c>
+      <c r="B116" t="n">
+        <v>1260.021</v>
+      </c>
+      <c r="C116" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1260.787</v>
+      </c>
+      <c r="B117" t="n">
+        <v>1262.054</v>
+      </c>
+      <c r="C117" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>1267.021</v>
+      </c>
+      <c r="B118" t="n">
+        <v>1268.654</v>
+      </c>
+      <c r="C118" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>1271.121</v>
+      </c>
+      <c r="B119" t="n">
+        <v>1272.787</v>
+      </c>
+      <c r="C119" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>1272.854</v>
+      </c>
+      <c r="B120" t="n">
+        <v>1273.687</v>
+      </c>
+      <c r="C120" t="n">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>1273.721</v>
+      </c>
+      <c r="B121" t="n">
+        <v>1274.987</v>
+      </c>
+      <c r="C121" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>1275.021</v>
+      </c>
+      <c r="B122" t="n">
+        <v>1275.487</v>
+      </c>
+      <c r="C122" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>1275.721</v>
+      </c>
+      <c r="B123" t="n">
+        <v>1276.987</v>
+      </c>
+      <c r="C123" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>1278.854</v>
+      </c>
+      <c r="B124" t="n">
+        <v>1279.587</v>
+      </c>
+      <c r="C124" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>1279.621</v>
+      </c>
+      <c r="B125" t="n">
+        <v>1280.054</v>
+      </c>
+      <c r="C125" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>1295.654</v>
+      </c>
+      <c r="B126" t="n">
+        <v>1296.987</v>
+      </c>
+      <c r="C126" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>1308.754</v>
+      </c>
+      <c r="B127" t="n">
+        <v>1310.32</v>
+      </c>
+      <c r="C127" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1310.387</v>
+      </c>
+      <c r="B128" t="n">
+        <v>1312.02</v>
+      </c>
+      <c r="C128" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>1312.087</v>
+      </c>
+      <c r="B129" t="n">
+        <v>1313.82</v>
+      </c>
+      <c r="C129" t="n">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>1313.854</v>
+      </c>
+      <c r="B130" t="n">
+        <v>1315.187</v>
+      </c>
+      <c r="C130" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>1330.92</v>
+      </c>
+      <c r="B131" t="n">
+        <v>1332.12</v>
+      </c>
+      <c r="C131" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>1332.153</v>
+      </c>
+      <c r="B132" t="n">
+        <v>1334.287</v>
+      </c>
+      <c r="C132" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>1334.42</v>
+      </c>
+      <c r="B133" t="n">
+        <v>1335.153</v>
+      </c>
+      <c r="C133" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>1336.62</v>
+      </c>
+      <c r="B134" t="n">
+        <v>1338.353</v>
+      </c>
+      <c r="C134" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>1338.42</v>
+      </c>
+      <c r="B135" t="n">
+        <v>1339.753</v>
+      </c>
+      <c r="C135" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>1339.787</v>
+      </c>
+      <c r="B136" t="n">
+        <v>1341.653</v>
+      </c>
+      <c r="C136" t="n">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>1341.82</v>
+      </c>
+      <c r="B137" t="n">
+        <v>1343.253</v>
+      </c>
+      <c r="C137" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>1343.32</v>
+      </c>
+      <c r="B138" t="n">
+        <v>1344.42</v>
+      </c>
+      <c r="C138" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>1353.153</v>
+      </c>
+      <c r="B139" t="n">
+        <v>1354.42</v>
+      </c>
+      <c r="C139" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>1354.453</v>
+      </c>
+      <c r="B140" t="n">
+        <v>1355.286</v>
+      </c>
+      <c r="C140" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>1355.32</v>
+      </c>
+      <c r="B141" t="n">
+        <v>1356.42</v>
+      </c>
+      <c r="C141" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>1357.02</v>
+      </c>
+      <c r="B142" t="n">
+        <v>1358.386</v>
+      </c>
+      <c r="C142" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>1358.453</v>
+      </c>
+      <c r="B143" t="n">
+        <v>1359.82</v>
+      </c>
+      <c r="C143" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>1359.853</v>
+      </c>
+      <c r="B144" t="n">
+        <v>1361.82</v>
+      </c>
+      <c r="C144" t="n">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>1361.853</v>
+      </c>
+      <c r="B145" t="n">
+        <v>1363.353</v>
+      </c>
+      <c r="C145" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>1363.42</v>
+      </c>
+      <c r="B146" t="n">
+        <v>1364.253</v>
+      </c>
+      <c r="C146" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>1368.853</v>
+      </c>
+      <c r="B147" t="n">
+        <v>1369.653</v>
+      </c>
+      <c r="C147" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>1369.72</v>
+      </c>
+      <c r="B148" t="n">
+        <v>1371.953</v>
+      </c>
+      <c r="C148" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>1372.053</v>
+      </c>
+      <c r="B149" t="n">
+        <v>1374.053</v>
+      </c>
+      <c r="C149" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>1374.12</v>
+      </c>
+      <c r="B150" t="n">
+        <v>1374.686</v>
+      </c>
+      <c r="C150" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>1374.72</v>
+      </c>
+      <c r="B151" t="n">
+        <v>1375.286</v>
+      </c>
+      <c r="C151" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>1375.353</v>
+      </c>
+      <c r="B152" t="n">
+        <v>1375.953</v>
+      </c>
+      <c r="C152" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>1375.986</v>
+      </c>
+      <c r="B153" t="n">
+        <v>1376.42</v>
+      </c>
+      <c r="C153" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>1376.486</v>
+      </c>
+      <c r="B154" t="n">
+        <v>1377.653</v>
+      </c>
+      <c r="C154" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>1377.72</v>
+      </c>
+      <c r="B155" t="n">
+        <v>1379.486</v>
+      </c>
+      <c r="C155" t="n">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>1381.42</v>
+      </c>
+      <c r="B156" t="n">
+        <v>1385.153</v>
+      </c>
+      <c r="C156" t="n">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>1385.219</v>
+      </c>
+      <c r="B157" t="n">
+        <v>1386.453</v>
+      </c>
+      <c r="C157" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>1386.486</v>
+      </c>
+      <c r="B158" t="n">
+        <v>1387.286</v>
+      </c>
+      <c r="C158" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>1387.919</v>
+      </c>
+      <c r="B159" t="n">
+        <v>1388.353</v>
+      </c>
+      <c r="C159" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>1388.419</v>
+      </c>
+      <c r="B160" t="n">
+        <v>1389.886</v>
+      </c>
+      <c r="C160" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>1390.919</v>
+      </c>
+      <c r="B161" t="n">
+        <v>1391.886</v>
+      </c>
+      <c r="C161" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>1395.719</v>
+      </c>
+      <c r="B162" t="n">
+        <v>1396.586</v>
+      </c>
+      <c r="C162" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>1397.319</v>
+      </c>
+      <c r="B163" t="n">
+        <v>1398.319</v>
+      </c>
+      <c r="C163" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>1398.353</v>
+      </c>
+      <c r="B164" t="n">
+        <v>1401.386</v>
+      </c>
+      <c r="C164" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>1401.453</v>
+      </c>
+      <c r="B165" t="n">
+        <v>1401.886</v>
+      </c>
+      <c r="C165" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>1401.919</v>
+      </c>
+      <c r="B166" t="n">
+        <v>1403.253</v>
+      </c>
+      <c r="C166" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>1403.919</v>
+      </c>
+      <c r="B167" t="n">
+        <v>1406.286</v>
+      </c>
+      <c r="C167" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>1408.853</v>
+      </c>
+      <c r="B168" t="n">
+        <v>1409.886</v>
+      </c>
+      <c r="C168" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>1421.919</v>
+      </c>
+      <c r="B169" t="n">
+        <v>1422.719</v>
+      </c>
+      <c r="C169" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>1422.752</v>
+      </c>
+      <c r="B170" t="n">
+        <v>1423.552</v>
+      </c>
+      <c r="C170" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>1426.919</v>
+      </c>
+      <c r="B171" t="n">
+        <v>1427.519</v>
+      </c>
+      <c r="C171" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>1428.052</v>
+      </c>
+      <c r="B172" t="n">
+        <v>1429.819</v>
+      </c>
+      <c r="C172" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>1429.886</v>
+      </c>
+      <c r="B173" t="n">
+        <v>1430.186</v>
+      </c>
+      <c r="C173" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>1432.819</v>
+      </c>
+      <c r="B174" t="n">
+        <v>1434.486</v>
+      </c>
+      <c r="C174" t="n">
+        <v>413</v>
       </c>
     </row>
   </sheetData>
